--- a/data/trans_orig/P44C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9778</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29012</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>42931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51024</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91409</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>124029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>32314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34194</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>40460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>57024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>70864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131283</t>
+          <t>130394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>164151</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6916,32 +6916,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6951,32 +6951,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17973</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -6994,32 +6994,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>19552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125961</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7029,32 +7029,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7064,32 +7064,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47483</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>38873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136045</t>
+          <t>59056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -7107,32 +7107,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>280022</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130720</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>315019</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7142,32 +7142,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7177,32 +7177,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>308522</t>
+          <t>67841</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158306</t>
+          <t>56334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373231</t>
+          <t>79248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -7220,32 +7220,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76646</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>36636</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92677</t>
+          <t>47672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7333,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>326538</t>
+          <t>86240</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326538</t>
+          <t>86240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326538</t>
+          <t>86240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67378</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67378</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67378</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7403,17 +7403,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>393916</t>
+          <t>158711</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393916</t>
+          <t>158711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393916</t>
+          <t>158711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7450,32 +7450,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>64363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>56168</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60134</t>
+          <t>65453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>108171</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86945</t>
+          <t>92562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116339</t>
+          <t>122747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -7676,32 +7676,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73320</t>
+          <t>79615</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61250</t>
+          <t>67105</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85672</t>
+          <t>92678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7711,32 +7711,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>70308</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>60865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69910</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>134179</t>
+          <t>149924</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120223</t>
+          <t>134083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149085</t>
+          <t>166073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43760</t>
+          <t>44564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>56647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7859,32 +7859,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74959</t>
+          <t>78226</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62733</t>
+          <t>65391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89047</t>
+          <t>92370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>174514</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174514</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174514</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7937,17 +7937,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>349540</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>349540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>349540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8019,32 +8019,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8054,32 +8054,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48039</t>
+          <t>49493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8167,32 +8167,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36737</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8202,32 +8202,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>79404</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64035</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86341</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -8245,32 +8245,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>84258</t>
+          <t>92545</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73782</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94064</t>
+          <t>103675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8280,32 +8280,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69345</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60675</t>
+          <t>67889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77901</t>
+          <t>85493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>153602</t>
+          <t>169631</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140353</t>
+          <t>154605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166954</t>
+          <t>183453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -8358,32 +8358,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8393,32 +8393,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20925</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8428,32 +8428,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>64468</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48481</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69084</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -8471,17 +8471,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>159268</t>
+          <t>172575</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>159268</t>
+          <t>172575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159268</t>
+          <t>172575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8506,17 +8506,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138762</t>
+          <t>152951</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138762</t>
+          <t>152951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138762</t>
+          <t>152951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>298029</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298029</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>298029</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -8701,32 +8701,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8736,32 +8736,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8771,32 +8771,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -8814,32 +8814,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>64496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8849,32 +8849,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>85454</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69102</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82452</t>
+          <t>91980</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8884,32 +8884,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135108</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124237</t>
+          <t>138704</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>145288</t>
+          <t>161406</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -8927,32 +8927,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8962,32 +8962,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8997,32 +8997,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9040,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9075,17 +9075,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>106331</t>
+          <t>117860</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106331</t>
+          <t>117860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106331</t>
+          <t>117860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>224642</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>224642</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>224642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9270,32 +9270,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>116336</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206265</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>123117</t>
+          <t>133678</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109523</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9340,32 +9340,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>269113</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144870</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331605</t>
+          <t>293577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -9383,32 +9383,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>496330</t>
+          <t>273817</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>364625</t>
+          <t>252038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>640739</t>
+          <t>294976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9418,32 +9418,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>235084</t>
+          <t>263528</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>246515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>250484</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9453,32 +9453,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>731413</t>
+          <t>537345</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>598928</t>
+          <t>510021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>952101</t>
+          <t>564019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -9496,32 +9496,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>104858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>169570</t>
+          <t>139404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9531,32 +9531,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>107921</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100041</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253406</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -9609,17 +9609,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9679,17 +9679,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
